--- a/ksoft_old/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
@@ -81561,13 +81561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C11A7B-E936-4AB1-A23D-6F0AD0C9E76B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE858D7-C4C7-4DBE-B320-73CA9858398A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7308344D-5166-471D-AE72-7EE6262D1C4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E6665FD-E29A-4054-B4E5-54BCDC6AD1EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFF8593E-3058-4681-ABE2-313BF8D77DFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D54A68C8-3DE9-4237-80BD-A3693D7F6723}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
@@ -81561,13 +81561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE858D7-C4C7-4DBE-B320-73CA9858398A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E5C0041-BF62-40BD-99A1-F1F171907C2B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E6665FD-E29A-4054-B4E5-54BCDC6AD1EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74452421-0CD5-4BF5-BD83-0BBFAF844D67}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D54A68C8-3DE9-4237-80BD-A3693D7F6723}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EFCB487-7EF5-4104-977E-909E0FB8439B}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
@@ -81561,13 +81561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E5C0041-BF62-40BD-99A1-F1F171907C2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47C11A7B-E936-4AB1-A23D-6F0AD0C9E76B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74452421-0CD5-4BF5-BD83-0BBFAF844D67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7308344D-5166-471D-AE72-7EE6262D1C4F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EFCB487-7EF5-4104-977E-909E0FB8439B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFF8593E-3058-4681-ABE2-313BF8D77DFE}"/>
 </file>